--- a/data/Resource Online Status Log_2026_02_05_10_21_49.xlsx
+++ b/data/Resource Online Status Log_2026_02_05_10_21_49.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD91ED47-BA5E-4E09-8653-7711FCC78563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CD36A84-D78C-419E-B901-708F62CE29FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1200" windowWidth="17280" windowHeight="9912" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resource Online or Offline Log" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="435">
   <si>
     <t>Name</t>
   </si>
@@ -211,7 +211,7 @@
     <t>2026-02-04 18:11:53</t>
   </si>
   <si>
-    <t>697:33:30</t>
+    <t>696:33:30</t>
   </si>
   <si>
     <t>C.AD01</t>
@@ -340,9 +340,21 @@
     <t>C.GH05</t>
   </si>
   <si>
+    <t>2026-02-10 18:23:58</t>
+  </si>
+  <si>
+    <t>7Times</t>
+  </si>
+  <si>
+    <t>02:00:26</t>
+  </si>
+  <si>
     <t>C.GH06</t>
   </si>
   <si>
+    <t>02:00:28</t>
+  </si>
+  <si>
     <t>C.HR01</t>
   </si>
   <si>
@@ -409,7 +421,7 @@
     <t>2026-02-04 18:08:50</t>
   </si>
   <si>
-    <t>697:38:32</t>
+    <t>696:38:32</t>
   </si>
   <si>
     <t>C.HR17</t>
@@ -445,9 +457,6 @@
     <t>2026-01-29 11:01:53</t>
   </si>
   <si>
-    <t>7Times</t>
-  </si>
-  <si>
     <t>02:03:29</t>
   </si>
   <si>
@@ -556,7 +565,7 @@
     <t>2026-02-04 18:14:55</t>
   </si>
   <si>
-    <t>697:38:53</t>
+    <t>696:38:53</t>
   </si>
   <si>
     <t>C.IW1 09</t>
@@ -817,10 +826,10 @@
     <t>2026-02-03 16:07:23</t>
   </si>
   <si>
-    <t>537:32:37</t>
-  </si>
-  <si>
-    <t>537:42:29</t>
+    <t>441:32:37</t>
+  </si>
+  <si>
+    <t>441:42:29</t>
   </si>
   <si>
     <t>C.LR16</t>
@@ -1096,13 +1105,13 @@
     <t>LPR</t>
   </si>
   <si>
-    <t>2026-02-04 07:48:48</t>
-  </si>
-  <si>
-    <t>19Times</t>
-  </si>
-  <si>
-    <t>89:07:05</t>
+    <t>2026-02-10 18:23:37</t>
+  </si>
+  <si>
+    <t>10Times</t>
+  </si>
+  <si>
+    <t>38:15:18</t>
   </si>
   <si>
     <t>Exit Gate</t>
@@ -1111,16 +1120,22 @@
     <t>192.168.14.141</t>
   </si>
   <si>
-    <t>2026-02-04 00:48:48</t>
-  </si>
-  <si>
-    <t>10:46:04</t>
+    <t>2026-02-10 11:23:37</t>
+  </si>
+  <si>
+    <t>9Times</t>
+  </si>
+  <si>
+    <t>10:49:13</t>
   </si>
   <si>
     <t>Frozen Recieve</t>
   </si>
   <si>
-    <t>365:35:00</t>
+    <t>2026-02-09 12:34:34</t>
+  </si>
+  <si>
+    <t>345:41:46</t>
   </si>
   <si>
     <t>FX3459879</t>
@@ -1228,7 +1243,7 @@
     <t>3Times</t>
   </si>
   <si>
-    <t>697:55:27</t>
+    <t>696:55:27</t>
   </si>
   <si>
     <t>High Risk Entry</t>
@@ -1243,7 +1258,7 @@
     <t>Office Side (Phase 2 CCTV)</t>
   </si>
   <si>
-    <t>697:28:57</t>
+    <t>696:28:57</t>
   </si>
   <si>
     <t>IPCamera 29</t>
@@ -1252,7 +1267,7 @@
     <t>2026-02-04 18:14:54</t>
   </si>
   <si>
-    <t>697:23:36</t>
+    <t>696:23:36</t>
   </si>
   <si>
     <t>IPdome 01</t>
@@ -1264,45 +1279,42 @@
     <t>IPdome 02</t>
   </si>
   <si>
-    <t>290:15:50</t>
-  </si>
-  <si>
-    <t>Loading Gate1</t>
-  </si>
-  <si>
-    <t>Low risk Entry</t>
+    <t>370:02:14</t>
+  </si>
+  <si>
+    <t>Low Risk in</t>
+  </si>
+  <si>
+    <t>11:15:45</t>
+  </si>
+  <si>
+    <t>MDB1-1</t>
+  </si>
+  <si>
+    <t>11:12:28</t>
+  </si>
+  <si>
+    <t>MDB1-2</t>
+  </si>
+  <si>
+    <t>11:12:15</t>
+  </si>
+  <si>
+    <t>Medium In</t>
+  </si>
+  <si>
+    <t>Out Gate</t>
+  </si>
+  <si>
+    <t>11:17:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parking </t>
   </si>
   <si>
     <t>11:15:27</t>
   </si>
   <si>
-    <t>Manager Parking</t>
-  </si>
-  <si>
-    <t>11:15:45</t>
-  </si>
-  <si>
-    <t>MDB1-1</t>
-  </si>
-  <si>
-    <t>11:12:28</t>
-  </si>
-  <si>
-    <t>MDB1-2</t>
-  </si>
-  <si>
-    <t>11:12:15</t>
-  </si>
-  <si>
-    <t>Out Gate</t>
-  </si>
-  <si>
-    <t>9Times</t>
-  </si>
-  <si>
-    <t>11:16:41</t>
-  </si>
-  <si>
     <t>Server Room</t>
   </si>
   <si>
@@ -1312,7 +1324,7 @@
     <t>Store Recieve</t>
   </si>
   <si>
-    <t>365:39:52</t>
+    <t>345:46:43</t>
   </si>
 </sst>
 </file>
@@ -1680,12 +1692,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G235"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="25.6640625" customWidth="1"/>
+    <col min="1" max="7" width="25.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1708,7 +1720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1731,7 +1743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1754,7 +1766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1777,7 +1789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -1800,7 +1812,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -1823,7 +1835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1846,7 +1858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -1869,7 +1881,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
@@ -1892,7 +1904,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -1915,7 +1927,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -1938,7 +1950,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
@@ -1961,7 +1973,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
@@ -1984,7 +1996,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>43</v>
       </c>
@@ -2007,7 +2019,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -2030,7 +2042,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
@@ -2053,7 +2065,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -2076,7 +2088,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>53</v>
       </c>
@@ -2099,7 +2111,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
@@ -2122,7 +2134,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>57</v>
       </c>
@@ -2145,7 +2157,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>58</v>
       </c>
@@ -2168,7 +2180,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
@@ -2191,7 +2203,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>64</v>
       </c>
@@ -2214,7 +2226,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>68</v>
       </c>
@@ -2237,7 +2249,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>69</v>
       </c>
@@ -2260,7 +2272,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>70</v>
       </c>
@@ -2283,7 +2295,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>71</v>
       </c>
@@ -2306,7 +2318,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>72</v>
       </c>
@@ -2329,7 +2341,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>73</v>
       </c>
@@ -2352,7 +2364,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>74</v>
       </c>
@@ -2375,7 +2387,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>75</v>
       </c>
@@ -2398,7 +2410,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>77</v>
       </c>
@@ -2421,7 +2433,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>79</v>
       </c>
@@ -2444,7 +2456,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -2467,7 +2479,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>84</v>
       </c>
@@ -2490,7 +2502,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>86</v>
       </c>
@@ -2513,7 +2525,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>88</v>
       </c>
@@ -2536,7 +2548,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>91</v>
       </c>
@@ -2559,7 +2571,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>93</v>
       </c>
@@ -2582,7 +2594,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>95</v>
       </c>
@@ -2605,7 +2617,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>97</v>
       </c>
@@ -2628,7 +2640,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>98</v>
       </c>
@@ -2651,7 +2663,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>99</v>
       </c>
@@ -2674,7 +2686,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>100</v>
       </c>
@@ -2697,7 +2709,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>101</v>
       </c>
@@ -2720,7 +2732,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>102</v>
       </c>
@@ -2743,7 +2755,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>104</v>
       </c>
@@ -2766,7 +2778,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>105</v>
       </c>
@@ -2780,18 +2792,18 @@
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>48</v>
@@ -2803,24 +2815,24 @@
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
@@ -2832,18 +2844,18 @@
         <v>29</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
@@ -2855,18 +2867,18 @@
         <v>29</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C52" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
@@ -2878,19 +2890,19 @@
         <v>29</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
@@ -2901,41 +2913,41 @@
         <v>29</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
@@ -2947,18 +2959,18 @@
         <v>29</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
@@ -2970,18 +2982,18 @@
         <v>29</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
@@ -2993,18 +3005,18 @@
         <v>29</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
@@ -3016,18 +3028,18 @@
         <v>29</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
@@ -3039,18 +3051,18 @@
         <v>29</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
@@ -3062,18 +3074,18 @@
         <v>29</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
@@ -3085,18 +3097,18 @@
         <v>29</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
@@ -3108,87 +3120,87 @@
         <v>29</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A65" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
@@ -3200,18 +3212,18 @@
         <v>29</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
@@ -3223,64 +3235,64 @@
         <v>29</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A69" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>10</v>
@@ -3292,18 +3304,18 @@
         <v>29</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
@@ -3315,18 +3327,18 @@
         <v>29</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
@@ -3338,18 +3350,18 @@
         <v>29</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
@@ -3361,18 +3373,18 @@
         <v>29</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
@@ -3384,18 +3396,18 @@
         <v>29</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
@@ -3407,18 +3419,18 @@
         <v>29</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
@@ -3430,18 +3442,18 @@
         <v>29</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
@@ -3453,64 +3465,64 @@
         <v>29</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="D79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F79" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
@@ -3522,64 +3534,64 @@
         <v>29</v>
       </c>
       <c r="G80" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A81" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
@@ -3591,41 +3603,41 @@
         <v>29</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F84" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
@@ -3637,662 +3649,662 @@
         <v>29</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A87" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B87" s="1" t="s">
+      <c r="F87" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A88" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="D91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F91" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F93" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F95" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F97" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F98" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F99" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F102" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F103" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F104" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F105" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F106" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F107" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F108" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F109" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F111" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>10</v>
@@ -4304,18 +4316,18 @@
         <v>29</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>10</v>
@@ -4327,18 +4339,18 @@
         <v>29</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>10</v>
@@ -4350,18 +4362,18 @@
         <v>29</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>10</v>
@@ -4373,18 +4385,18 @@
         <v>29</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>10</v>
@@ -4396,18 +4408,18 @@
         <v>29</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>10</v>
@@ -4419,18 +4431,18 @@
         <v>29</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>10</v>
@@ -4445,15 +4457,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>10</v>
@@ -4465,18 +4477,18 @@
         <v>29</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>10</v>
@@ -4488,18 +4500,18 @@
         <v>29</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>10</v>
@@ -4511,18 +4523,18 @@
         <v>29</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>10</v>
@@ -4534,18 +4546,18 @@
         <v>29</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>10</v>
@@ -4557,18 +4569,18 @@
         <v>29</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>10</v>
@@ -4580,18 +4592,18 @@
         <v>29</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>10</v>
@@ -4606,15 +4618,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>10</v>
@@ -4629,15 +4641,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>10</v>
@@ -4649,18 +4661,18 @@
         <v>29</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>10</v>
@@ -4672,18 +4684,18 @@
         <v>29</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>10</v>
@@ -4695,18 +4707,18 @@
         <v>29</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>10</v>
@@ -4718,18 +4730,18 @@
         <v>29</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>10</v>
@@ -4741,18 +4753,18 @@
         <v>29</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>10</v>
@@ -4764,18 +4776,18 @@
         <v>29</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>10</v>
@@ -4787,18 +4799,18 @@
         <v>29</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C136" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>10</v>
@@ -4810,19 +4822,19 @@
         <v>29</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="D137" s="1" t="s">
         <v>10</v>
       </c>
@@ -4833,18 +4845,18 @@
         <v>29</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>10</v>
@@ -4856,18 +4868,18 @@
         <v>29</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>10</v>
@@ -4879,18 +4891,18 @@
         <v>29</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>10</v>
@@ -4902,18 +4914,18 @@
         <v>29</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>10</v>
@@ -4925,18 +4937,18 @@
         <v>29</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>10</v>
@@ -4948,18 +4960,18 @@
         <v>29</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>10</v>
@@ -4971,18 +4983,18 @@
         <v>29</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>10</v>
@@ -4994,64 +5006,64 @@
         <v>29</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>10</v>
@@ -5063,18 +5075,18 @@
         <v>29</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>10</v>
@@ -5086,18 +5098,18 @@
         <v>29</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>10</v>
@@ -5109,18 +5121,18 @@
         <v>29</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>10</v>
@@ -5132,18 +5144,18 @@
         <v>29</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>10</v>
@@ -5155,18 +5167,18 @@
         <v>29</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>10</v>
@@ -5178,18 +5190,18 @@
         <v>29</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>10</v>
@@ -5201,18 +5213,18 @@
         <v>29</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>10</v>
@@ -5224,18 +5236,18 @@
         <v>29</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>10</v>
@@ -5247,18 +5259,18 @@
         <v>29</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>10</v>
@@ -5270,18 +5282,18 @@
         <v>29</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>10</v>
@@ -5293,18 +5305,18 @@
         <v>29</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>10</v>
@@ -5316,18 +5328,18 @@
         <v>29</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>10</v>
@@ -5339,18 +5351,18 @@
         <v>29</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>10</v>
@@ -5362,18 +5374,18 @@
         <v>29</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>10</v>
@@ -5385,18 +5397,18 @@
         <v>29</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>10</v>
@@ -5408,18 +5420,18 @@
         <v>29</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>10</v>
@@ -5431,18 +5443,18 @@
         <v>29</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>10</v>
@@ -5454,18 +5466,18 @@
         <v>29</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>10</v>
@@ -5477,18 +5489,18 @@
         <v>29</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>10</v>
@@ -5500,18 +5512,18 @@
         <v>29</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>10</v>
@@ -5523,18 +5535,18 @@
         <v>29</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>10</v>
@@ -5546,18 +5558,18 @@
         <v>29</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>10</v>
@@ -5569,18 +5581,18 @@
         <v>29</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>10</v>
@@ -5592,18 +5604,18 @@
         <v>29</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>10</v>
@@ -5615,18 +5627,18 @@
         <v>29</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>10</v>
@@ -5638,18 +5650,18 @@
         <v>29</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>10</v>
@@ -5661,18 +5673,18 @@
         <v>29</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>10</v>
@@ -5684,18 +5696,18 @@
         <v>29</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>10</v>
@@ -5707,18 +5719,18 @@
         <v>29</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>10</v>
@@ -5733,15 +5745,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>10</v>
@@ -5756,15 +5768,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>10</v>
@@ -5779,15 +5791,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>10</v>
@@ -5802,15 +5814,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>10</v>
@@ -5825,15 +5837,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>10</v>
@@ -5845,18 +5857,18 @@
         <v>29</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>10</v>
@@ -5868,18 +5880,18 @@
         <v>29</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>10</v>
@@ -5891,18 +5903,18 @@
         <v>29</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>10</v>
@@ -5914,18 +5926,18 @@
         <v>29</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>10</v>
@@ -5937,18 +5949,18 @@
         <v>29</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>10</v>
@@ -5960,18 +5972,18 @@
         <v>29</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>10</v>
@@ -5983,18 +5995,18 @@
         <v>29</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>10</v>
@@ -6006,18 +6018,18 @@
         <v>29</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>10</v>
@@ -6029,18 +6041,18 @@
         <v>29</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>10</v>
@@ -6052,18 +6064,18 @@
         <v>29</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>10</v>
@@ -6075,18 +6087,18 @@
         <v>29</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>10</v>
@@ -6098,18 +6110,18 @@
         <v>29</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>10</v>
@@ -6121,18 +6133,18 @@
         <v>29</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>10</v>
@@ -6144,18 +6156,18 @@
         <v>29</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>10</v>
@@ -6167,18 +6179,18 @@
         <v>29</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>10</v>
@@ -6190,18 +6202,18 @@
         <v>29</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>10</v>
@@ -6213,18 +6225,18 @@
         <v>29</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>10</v>
@@ -6236,18 +6248,18 @@
         <v>29</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>10</v>
@@ -6259,18 +6271,18 @@
         <v>29</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>10</v>
@@ -6282,18 +6294,18 @@
         <v>29</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>10</v>
@@ -6305,231 +6317,231 @@
         <v>29</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G202" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A203" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A203" s="1" t="s">
+      <c r="C203" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="D203" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G203" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A204" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A204" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="F204" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G205" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A206" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F206" s="1" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A206" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="G206" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G208" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A209" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A209" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="D209" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>160</v>
+        <v>367</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>12</v>
@@ -6538,38 +6550,38 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>10</v>
@@ -6584,38 +6596,38 @@
         <v>16</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B215" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>10</v>
@@ -6627,24 +6639,24 @@
         <v>12</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>12</v>
@@ -6653,36 +6665,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A217" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E217" s="1"/>
       <c r="F217" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A218" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>10</v>
@@ -6694,24 +6706,24 @@
         <v>12</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A219" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>12</v>
@@ -6720,15 +6732,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A220" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>10</v>
@@ -6740,87 +6752,87 @@
         <v>12</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A221" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A223" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A224" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>61</v>
@@ -6832,222 +6844,222 @@
         <v>12</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A225" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A226" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A227" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A228" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A229" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A230" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A231" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A232" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A233" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>425</v>
+        <v>163</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A234" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>19</v>
@@ -7062,30 +7074,30 @@
         <v>29</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A235" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
